--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-29.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-29.xlsx
@@ -1309,7 +1309,7 @@
     <t>Universitario de Deportes</t>
   </si>
   <si>
-    <t>2026-08-27 01:57:44</t>
+    <t>2026-08-27 04:12:49</t>
   </si>
 </sst>
 </file>
@@ -1906,157 +1906,157 @@
         <v>2.38</v>
       </c>
       <c r="G2">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="H2">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="I2">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J2">
         <v>2.92</v>
       </c>
       <c r="K2">
-        <v>3.85</v>
+        <v>3.6</v>
       </c>
       <c r="L2">
+        <v>1.49</v>
+      </c>
+      <c r="M2">
+        <v>1.12</v>
+      </c>
+      <c r="N2">
+        <v>2.62</v>
+      </c>
+      <c r="O2">
+        <v>1.5</v>
+      </c>
+      <c r="P2">
+        <v>1.53</v>
+      </c>
+      <c r="Q2">
+        <v>2.52</v>
+      </c>
+      <c r="R2">
+        <v>1.19</v>
+      </c>
+      <c r="S2">
+        <v>5.1</v>
+      </c>
+      <c r="T2">
+        <v>2.02</v>
+      </c>
+      <c r="U2">
+        <v>1.78</v>
+      </c>
+      <c r="V2">
+        <v>1.35</v>
+      </c>
+      <c r="W2">
+        <v>1.59</v>
+      </c>
+      <c r="X2">
+        <v>10.5</v>
+      </c>
+      <c r="Y2">
+        <v>11.5</v>
+      </c>
+      <c r="Z2">
+        <v>27</v>
+      </c>
+      <c r="AA2">
+        <v>85</v>
+      </c>
+      <c r="AB2">
+        <v>9</v>
+      </c>
+      <c r="AC2">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD2">
+        <v>18</v>
+      </c>
+      <c r="AE2">
+        <v>65</v>
+      </c>
+      <c r="AF2">
+        <v>17.5</v>
+      </c>
+      <c r="AG2">
+        <v>14.5</v>
+      </c>
+      <c r="AH2">
+        <v>26</v>
+      </c>
+      <c r="AI2">
+        <v>90</v>
+      </c>
+      <c r="AJ2">
+        <v>46</v>
+      </c>
+      <c r="AK2">
+        <v>42</v>
+      </c>
+      <c r="AL2">
+        <v>75</v>
+      </c>
+      <c r="AM2">
+        <v>200</v>
+      </c>
+      <c r="AN2">
+        <v>44</v>
+      </c>
+      <c r="AO2">
+        <v>85</v>
+      </c>
+      <c r="AP2">
+        <v>6.8</v>
+      </c>
+      <c r="AQ2">
+        <v>7.8</v>
+      </c>
+      <c r="AR2">
+        <v>17.5</v>
+      </c>
+      <c r="AS2">
         <v>1.01</v>
       </c>
-      <c r="M2">
+      <c r="AT2">
+        <v>6</v>
+      </c>
+      <c r="AU2">
+        <v>5.6</v>
+      </c>
+      <c r="AV2">
+        <v>12</v>
+      </c>
+      <c r="AW2">
         <v>1.01</v>
       </c>
-      <c r="N2">
+      <c r="AX2">
+        <v>11.5</v>
+      </c>
+      <c r="AY2">
+        <v>9.6</v>
+      </c>
+      <c r="AZ2">
+        <v>17</v>
+      </c>
+      <c r="BA2">
         <v>1.01</v>
       </c>
-      <c r="O2">
-        <v>1.02</v>
-      </c>
-      <c r="P2">
-        <v>1.46</v>
-      </c>
-      <c r="Q2">
-        <v>2</v>
-      </c>
-      <c r="R2">
-        <v>1.18</v>
-      </c>
-      <c r="S2">
+      <c r="BB2">
         <v>1.01</v>
       </c>
-      <c r="T2">
+      <c r="BC2">
         <v>1.01</v>
       </c>
-      <c r="U2">
+      <c r="BD2">
         <v>1.01</v>
       </c>
-      <c r="V2">
-        <v>1.33</v>
-      </c>
-      <c r="W2">
-        <v>1.57</v>
-      </c>
-      <c r="X2">
-        <v>1000</v>
-      </c>
-      <c r="Y2">
-        <v>1000</v>
-      </c>
-      <c r="Z2">
-        <v>1000</v>
-      </c>
-      <c r="AA2">
-        <v>1000</v>
-      </c>
-      <c r="AB2">
-        <v>1000</v>
-      </c>
-      <c r="AC2">
-        <v>1000</v>
-      </c>
-      <c r="AD2">
-        <v>1000</v>
-      </c>
-      <c r="AE2">
-        <v>1000</v>
-      </c>
-      <c r="AF2">
-        <v>1000</v>
-      </c>
-      <c r="AG2">
-        <v>1000</v>
-      </c>
-      <c r="AH2">
-        <v>1000</v>
-      </c>
-      <c r="AI2">
-        <v>1000</v>
-      </c>
-      <c r="AJ2">
-        <v>1000</v>
-      </c>
-      <c r="AK2">
-        <v>1000</v>
-      </c>
-      <c r="AL2">
-        <v>1000</v>
-      </c>
-      <c r="AM2">
-        <v>1000</v>
-      </c>
-      <c r="AN2">
-        <v>1000</v>
-      </c>
-      <c r="AO2">
-        <v>1000</v>
-      </c>
-      <c r="AP2">
-        <v>1.03</v>
-      </c>
-      <c r="AQ2">
-        <v>1.03</v>
-      </c>
-      <c r="AR2">
-        <v>1.03</v>
-      </c>
-      <c r="AS2">
-        <v>1.03</v>
-      </c>
-      <c r="AT2">
-        <v>1.03</v>
-      </c>
-      <c r="AU2">
-        <v>1.03</v>
-      </c>
-      <c r="AV2">
-        <v>1.03</v>
-      </c>
-      <c r="AW2">
-        <v>1.03</v>
-      </c>
-      <c r="AX2">
-        <v>1.03</v>
-      </c>
-      <c r="AY2">
-        <v>1.03</v>
-      </c>
-      <c r="AZ2">
-        <v>1.03</v>
-      </c>
-      <c r="BA2">
-        <v>1.03</v>
-      </c>
-      <c r="BB2">
-        <v>1.03</v>
-      </c>
-      <c r="BC2">
-        <v>1.03</v>
-      </c>
-      <c r="BD2">
-        <v>1.03</v>
-      </c>
       <c r="BE2">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF2">
         <v>1.01</v>
@@ -2065,64 +2065,64 @@
         <v>1.01</v>
       </c>
       <c r="BH2">
-        <v>3.2</v>
+        <v>2.82</v>
       </c>
       <c r="BI2">
-        <v>2.22</v>
+        <v>2.32</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK2">
-        <v>1.47</v>
+        <v>5.5</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.47</v>
+        <v>10</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="BO2">
-        <v>1.47</v>
+        <v>4.1</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BQ2">
-        <v>1.47</v>
+        <v>7.2</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS2">
-        <v>1.47</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BU2">
-        <v>1.47</v>
+        <v>5.1</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BW2">
-        <v>1.47</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY2">
-        <v>1.47</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ2">
         <v>1000</v>
       </c>
       <c r="CA2">
-        <v>1.47</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB2" t="s">
         <v>431</v>
@@ -2145,10 +2145,10 @@
         <v>296</v>
       </c>
       <c r="F3">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="G3">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="H3">
         <v>5.2</v>
@@ -2157,7 +2157,7 @@
         <v>6.2</v>
       </c>
       <c r="J3">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K3">
         <v>3.5</v>
@@ -2175,10 +2175,10 @@
         <v>0</v>
       </c>
       <c r="P3">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="Q3">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -2387,154 +2387,154 @@
         <v>297</v>
       </c>
       <c r="F4">
-        <v>1.04</v>
+        <v>1.93</v>
       </c>
       <c r="G4">
-        <v>1000</v>
+        <v>2.28</v>
       </c>
       <c r="H4">
-        <v>1.04</v>
+        <v>4</v>
       </c>
       <c r="I4">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="J4">
-        <v>1.04</v>
+        <v>2.86</v>
       </c>
       <c r="K4">
-        <v>950</v>
+        <v>3.85</v>
       </c>
       <c r="L4">
+        <v>1.47</v>
+      </c>
+      <c r="M4">
+        <v>1.11</v>
+      </c>
+      <c r="N4">
+        <v>2.48</v>
+      </c>
+      <c r="O4">
+        <v>1.43</v>
+      </c>
+      <c r="P4">
+        <v>1.5</v>
+      </c>
+      <c r="Q4">
+        <v>2.28</v>
+      </c>
+      <c r="R4">
+        <v>1.2</v>
+      </c>
+      <c r="S4">
+        <v>1.53</v>
+      </c>
+      <c r="T4">
+        <v>2.08</v>
+      </c>
+      <c r="U4">
+        <v>1.66</v>
+      </c>
+      <c r="V4">
+        <v>1.2</v>
+      </c>
+      <c r="W4">
+        <v>1.78</v>
+      </c>
+      <c r="X4">
+        <v>11</v>
+      </c>
+      <c r="Y4">
+        <v>15</v>
+      </c>
+      <c r="Z4">
+        <v>42</v>
+      </c>
+      <c r="AA4">
+        <v>160</v>
+      </c>
+      <c r="AB4">
+        <v>7.8</v>
+      </c>
+      <c r="AC4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD4">
+        <v>24</v>
+      </c>
+      <c r="AE4">
+        <v>100</v>
+      </c>
+      <c r="AF4">
+        <v>13</v>
+      </c>
+      <c r="AG4">
+        <v>13</v>
+      </c>
+      <c r="AH4">
+        <v>28</v>
+      </c>
+      <c r="AI4">
+        <v>120</v>
+      </c>
+      <c r="AJ4">
+        <v>30</v>
+      </c>
+      <c r="AK4">
+        <v>32</v>
+      </c>
+      <c r="AL4">
+        <v>65</v>
+      </c>
+      <c r="AM4">
+        <v>220</v>
+      </c>
+      <c r="AN4">
+        <v>28</v>
+      </c>
+      <c r="AO4">
+        <v>160</v>
+      </c>
+      <c r="AP4">
         <v>1.01</v>
       </c>
-      <c r="M4">
+      <c r="AQ4">
         <v>1.01</v>
       </c>
-      <c r="N4">
-        <v>1.26</v>
-      </c>
-      <c r="O4">
-        <v>1.02</v>
-      </c>
-      <c r="P4">
-        <v>1.25</v>
-      </c>
-      <c r="Q4">
-        <v>1.51</v>
-      </c>
-      <c r="R4">
-        <v>1.13</v>
-      </c>
-      <c r="S4">
-        <v>1.51</v>
-      </c>
-      <c r="T4">
+      <c r="AR4">
         <v>1.01</v>
-      </c>
-      <c r="U4">
-        <v>1.01</v>
-      </c>
-      <c r="V4">
-        <v>1.01</v>
-      </c>
-      <c r="W4">
-        <v>1.01</v>
-      </c>
-      <c r="X4">
-        <v>1000</v>
-      </c>
-      <c r="Y4">
-        <v>1000</v>
-      </c>
-      <c r="Z4">
-        <v>1000</v>
-      </c>
-      <c r="AA4">
-        <v>1000</v>
-      </c>
-      <c r="AB4">
-        <v>1000</v>
-      </c>
-      <c r="AC4">
-        <v>1000</v>
-      </c>
-      <c r="AD4">
-        <v>1000</v>
-      </c>
-      <c r="AE4">
-        <v>1000</v>
-      </c>
-      <c r="AF4">
-        <v>1000</v>
-      </c>
-      <c r="AG4">
-        <v>1000</v>
-      </c>
-      <c r="AH4">
-        <v>1000</v>
-      </c>
-      <c r="AI4">
-        <v>1000</v>
-      </c>
-      <c r="AJ4">
-        <v>1000</v>
-      </c>
-      <c r="AK4">
-        <v>1000</v>
-      </c>
-      <c r="AL4">
-        <v>1000</v>
-      </c>
-      <c r="AM4">
-        <v>1000</v>
-      </c>
-      <c r="AN4">
-        <v>1000</v>
-      </c>
-      <c r="AO4">
-        <v>1000</v>
-      </c>
-      <c r="AP4">
-        <v>1.03</v>
-      </c>
-      <c r="AQ4">
-        <v>1.03</v>
-      </c>
-      <c r="AR4">
-        <v>1.03</v>
       </c>
       <c r="AS4">
         <v>1.03</v>
       </c>
       <c r="AT4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW4">
         <v>1.03</v>
       </c>
       <c r="AX4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA4">
         <v>1.03</v>
       </c>
       <c r="BB4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC4">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD4">
         <v>1.03</v>
@@ -2549,58 +2549,58 @@
         <v>1.01</v>
       </c>
       <c r="BH4">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI4">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BJ4">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK4">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BN4">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BO4">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="BP4">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="BQ4">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BR4">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS4">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BT4">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="BU4">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="BV4">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW4">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BX4">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BY4">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -2632,16 +2632,16 @@
         <v>2.56</v>
       </c>
       <c r="G5">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="H5">
         <v>2.82</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J5">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K5">
         <v>3.75</v>
@@ -2653,7 +2653,7 @@
         <v>1.06</v>
       </c>
       <c r="N5">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O5">
         <v>1.29</v>
@@ -2677,7 +2677,7 @@
         <v>2.32</v>
       </c>
       <c r="V5">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W5">
         <v>1.57</v>
@@ -2722,7 +2722,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL5">
         <v>42</v>
@@ -2761,7 +2761,7 @@
         <v>20</v>
       </c>
       <c r="AX5">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AY5">
         <v>10</v>
@@ -2871,19 +2871,19 @@
         <v>299</v>
       </c>
       <c r="F6">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="G6">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="H6">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="I6">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="J6">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K6">
         <v>4.6</v>
@@ -2892,10 +2892,10 @@
         <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N6">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="O6">
         <v>1.24</v>
@@ -2904,133 +2904,133 @@
         <v>2.24</v>
       </c>
       <c r="Q6">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R6">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="S6">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="T6">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="U6">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="V6">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="W6">
         <v>1.35</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AP6">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="AQ6">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AR6">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AS6">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AT6">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AU6">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AV6">
-        <v>1.03</v>
+        <v>9.4</v>
       </c>
       <c r="AW6">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AX6">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AY6">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AZ6">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BA6">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="BB6">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BC6">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BD6">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="BE6">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -3113,166 +3113,166 @@
         <v>300</v>
       </c>
       <c r="F7">
-        <v>2.06</v>
+        <v>2.28</v>
       </c>
       <c r="G7">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="H7">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="I7">
-        <v>4.5</v>
+        <v>3.65</v>
       </c>
       <c r="J7">
-        <v>2.44</v>
+        <v>3.4</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>3.75</v>
       </c>
       <c r="L7">
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N7">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O7">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P7">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q7">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R7">
-        <v>1.18</v>
+        <v>1.35</v>
       </c>
       <c r="S7">
-        <v>1.86</v>
+        <v>3.35</v>
       </c>
       <c r="T7">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="U7">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V7">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="W7">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y7">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB7">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC7">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF7">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG7">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH7">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI7">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ7">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK7">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL7">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM7">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN7">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO7">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP7">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AQ7">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AR7">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AS7">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AT7">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AU7">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AV7">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AW7">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AX7">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AY7">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ7">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BA7">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BB7">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BC7">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BD7">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BE7">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF7">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BG7">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -3361,16 +3361,16 @@
         <v>2.9</v>
       </c>
       <c r="H8">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I8">
-        <v>2.9</v>
+        <v>2.76</v>
       </c>
       <c r="J8">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="K8">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -3385,10 +3385,10 @@
         <v>0</v>
       </c>
       <c r="P8">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q8">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -4081,13 +4081,13 @@
         <v>304</v>
       </c>
       <c r="F11">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="G11">
         <v>3.55</v>
       </c>
       <c r="H11">
-        <v>2.04</v>
+        <v>2.26</v>
       </c>
       <c r="I11">
         <v>2.58</v>
@@ -4096,7 +4096,7 @@
         <v>3.55</v>
       </c>
       <c r="K11">
-        <v>950</v>
+        <v>4.5</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -4111,7 +4111,7 @@
         <v>0</v>
       </c>
       <c r="P11">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q11">
         <v>1.86</v>
@@ -4323,22 +4323,22 @@
         <v>305</v>
       </c>
       <c r="F12">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="G12">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="H12">
         <v>2.22</v>
       </c>
       <c r="I12">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="J12">
         <v>3.3</v>
       </c>
       <c r="K12">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -4353,10 +4353,10 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q12">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -4595,10 +4595,10 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="Q13">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -4807,22 +4807,22 @@
         <v>307</v>
       </c>
       <c r="F14">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="G14">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="H14">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I14">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="J14">
         <v>2.98</v>
       </c>
       <c r="K14">
-        <v>4.3</v>
+        <v>3.75</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -4837,10 +4837,10 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q14">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -5049,19 +5049,19 @@
         <v>308</v>
       </c>
       <c r="F15">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="G15">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="H15">
-        <v>2.66</v>
+        <v>2.74</v>
       </c>
       <c r="I15">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="J15">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="K15">
         <v>4.3</v>
@@ -5079,7 +5079,7 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>1.25</v>
+        <v>2.48</v>
       </c>
       <c r="Q15">
         <v>1.58</v>
@@ -5321,7 +5321,7 @@
         <v>0</v>
       </c>
       <c r="P16">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="Q16">
         <v>1.55</v>
@@ -5563,7 +5563,7 @@
         <v>0</v>
       </c>
       <c r="P17">
-        <v>2.62</v>
+        <v>2.38</v>
       </c>
       <c r="Q17">
         <v>1.53</v>
@@ -5775,22 +5775,22 @@
         <v>311</v>
       </c>
       <c r="F18">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G18">
         <v>2.06</v>
       </c>
       <c r="H18">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="I18">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="J18">
         <v>3.4</v>
       </c>
       <c r="K18">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -5805,10 +5805,10 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="Q18">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -6017,7 +6017,7 @@
         <v>312</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="G19">
         <v>2.16</v>
@@ -6047,7 +6047,7 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>3.1</v>
+        <v>2.74</v>
       </c>
       <c r="Q19">
         <v>1.4</v>
@@ -6301,10 +6301,10 @@
         <v>2.62</v>
       </c>
       <c r="T20">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U20">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="V20">
         <v>0</v>
@@ -6412,7 +6412,7 @@
         <v>26</v>
       </c>
       <c r="BE20">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="BF20">
         <v>5.9</v>
@@ -6421,64 +6421,64 @@
         <v>70</v>
       </c>
       <c r="BH20">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BI20">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="BJ20">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK20">
         <v>5.5</v>
       </c>
       <c r="BL20">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM20">
         <v>21</v>
       </c>
       <c r="BN20">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO20">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="BP20">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BQ20">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
       <c r="BR20">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BS20">
-        <v>5.5</v>
+        <v>6.8</v>
       </c>
       <c r="BT20">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU20">
         <v>6.2</v>
       </c>
       <c r="BV20">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW20">
         <v>11.5</v>
       </c>
       <c r="BX20">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY20">
         <v>11.5</v>
       </c>
       <c r="BZ20">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="CA20">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="CB20" t="s">
         <v>431</v>
@@ -6501,10 +6501,10 @@
         <v>314</v>
       </c>
       <c r="F21">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="G21">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="H21">
         <v>3.25</v>
@@ -6531,7 +6531,7 @@
         <v>0</v>
       </c>
       <c r="P21">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q21">
         <v>2.12</v>
@@ -6746,13 +6746,13 @@
         <v>1.54</v>
       </c>
       <c r="G22">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="H22">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="I22">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J22">
         <v>4.6</v>
@@ -6988,16 +6988,16 @@
         <v>1.81</v>
       </c>
       <c r="G23">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="H23">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I23">
         <v>4.9</v>
       </c>
       <c r="J23">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="K23">
         <v>4.2</v>
@@ -7024,7 +7024,7 @@
         <v>1.41</v>
       </c>
       <c r="S23">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T23">
         <v>1.85</v>
@@ -7039,10 +7039,10 @@
         <v>0</v>
       </c>
       <c r="X23">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y23">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Z23">
         <v>70</v>
@@ -7057,7 +7057,7 @@
         <v>9</v>
       </c>
       <c r="AD23">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AE23">
         <v>700</v>
@@ -7105,7 +7105,7 @@
         <v>12</v>
       </c>
       <c r="AT23">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU23">
         <v>8</v>
@@ -7123,7 +7123,7 @@
         <v>9.4</v>
       </c>
       <c r="AZ23">
-        <v>14.5</v>
+        <v>17</v>
       </c>
       <c r="BA23">
         <v>32</v>
@@ -7138,7 +7138,7 @@
         <v>22</v>
       </c>
       <c r="BE23">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BF23">
         <v>9.6</v>
@@ -7156,13 +7156,13 @@
         <v>10</v>
       </c>
       <c r="BK23">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL23">
         <v>1000</v>
       </c>
       <c r="BM23">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BN23">
         <v>4.4</v>
@@ -7174,7 +7174,7 @@
         <v>12</v>
       </c>
       <c r="BQ23">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR23">
         <v>26</v>
@@ -7183,7 +7183,7 @@
         <v>10</v>
       </c>
       <c r="BT23">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU23">
         <v>5.7</v>
@@ -7192,19 +7192,19 @@
         <v>1000</v>
       </c>
       <c r="BW23">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BX23">
         <v>1000</v>
       </c>
       <c r="BY23">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ23">
         <v>21</v>
       </c>
       <c r="CA23">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="CB23" t="s">
         <v>431</v>
@@ -7236,13 +7236,13 @@
         <v>8.6</v>
       </c>
       <c r="I24">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J24">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="K24">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -7469,13 +7469,13 @@
         <v>318</v>
       </c>
       <c r="F25">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="G25">
         <v>2.9</v>
       </c>
       <c r="H25">
-        <v>1.09</v>
+        <v>2.78</v>
       </c>
       <c r="I25">
         <v>3.1</v>
@@ -7484,7 +7484,7 @@
         <v>3.35</v>
       </c>
       <c r="K25">
-        <v>950</v>
+        <v>3.65</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -7499,7 +7499,7 @@
         <v>0</v>
       </c>
       <c r="P25">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="Q25">
         <v>2.06</v>
@@ -7711,22 +7711,22 @@
         <v>319</v>
       </c>
       <c r="F26">
-        <v>1.46</v>
+        <v>2.66</v>
       </c>
       <c r="G26">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H26">
         <v>2.72</v>
       </c>
       <c r="I26">
-        <v>17.5</v>
+        <v>3.1</v>
       </c>
       <c r="J26">
         <v>3.15</v>
       </c>
       <c r="K26">
-        <v>950</v>
+        <v>3.9</v>
       </c>
       <c r="L26">
         <v>0</v>
@@ -7741,7 +7741,7 @@
         <v>0</v>
       </c>
       <c r="P26">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="Q26">
         <v>2.06</v>
@@ -7953,22 +7953,22 @@
         <v>320</v>
       </c>
       <c r="F27">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="G27">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="H27">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="I27">
-        <v>40</v>
+        <v>8.4</v>
       </c>
       <c r="J27">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="K27">
-        <v>9.800000000000001</v>
+        <v>5.4</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -7983,10 +7983,10 @@
         <v>0</v>
       </c>
       <c r="P27">
-        <v>2.06</v>
+        <v>2.24</v>
       </c>
       <c r="Q27">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -8198,7 +8198,7 @@
         <v>1.91</v>
       </c>
       <c r="G28">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="H28">
         <v>3.85</v>
@@ -8440,13 +8440,13 @@
         <v>2.94</v>
       </c>
       <c r="G29">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="H29">
         <v>2.12</v>
       </c>
       <c r="I29">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="J29">
         <v>3.8</v>
@@ -8679,22 +8679,22 @@
         <v>323</v>
       </c>
       <c r="F30">
-        <v>1.14</v>
+        <v>1.48</v>
       </c>
       <c r="G30">
         <v>1.59</v>
       </c>
       <c r="H30">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="I30">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="J30">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="K30">
-        <v>950</v>
+        <v>5.6</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -8709,10 +8709,10 @@
         <v>0</v>
       </c>
       <c r="P30">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="Q30">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -8921,22 +8921,22 @@
         <v>324</v>
       </c>
       <c r="F31">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="G31">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="H31">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="I31">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="J31">
         <v>3.6</v>
       </c>
       <c r="K31">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -8951,10 +8951,10 @@
         <v>0</v>
       </c>
       <c r="P31">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="Q31">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="R31">
         <v>0</v>
@@ -9408,16 +9408,16 @@
         <v>2.36</v>
       </c>
       <c r="G33">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="H33">
         <v>2.86</v>
       </c>
       <c r="I33">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="J33">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K33">
         <v>4.5</v>
@@ -9435,10 +9435,10 @@
         <v>0</v>
       </c>
       <c r="P33">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q33">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -10131,40 +10131,40 @@
         <v>329</v>
       </c>
       <c r="F36">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="G36">
-        <v>5.3</v>
+        <v>4.5</v>
       </c>
       <c r="H36">
+        <v>1.96</v>
+      </c>
+      <c r="I36">
+        <v>2.18</v>
+      </c>
+      <c r="J36">
+        <v>3.4</v>
+      </c>
+      <c r="K36">
+        <v>4.3</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>1.88</v>
+      </c>
+      <c r="Q36">
         <v>1.92</v>
-      </c>
-      <c r="I36">
-        <v>2.38</v>
-      </c>
-      <c r="J36">
-        <v>3.35</v>
-      </c>
-      <c r="K36">
-        <v>5.6</v>
-      </c>
-      <c r="L36">
-        <v>0</v>
-      </c>
-      <c r="M36">
-        <v>0</v>
-      </c>
-      <c r="N36">
-        <v>0</v>
-      </c>
-      <c r="O36">
-        <v>0</v>
-      </c>
-      <c r="P36">
-        <v>1.74</v>
-      </c>
-      <c r="Q36">
-        <v>1.81</v>
       </c>
       <c r="R36">
         <v>0</v>
@@ -10373,22 +10373,22 @@
         <v>330</v>
       </c>
       <c r="F37">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="G37">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="H37">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="I37">
-        <v>13</v>
+        <v>7.2</v>
       </c>
       <c r="J37">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K37">
-        <v>11</v>
+        <v>5.8</v>
       </c>
       <c r="L37">
         <v>0</v>
@@ -10403,10 +10403,10 @@
         <v>0</v>
       </c>
       <c r="P37">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="Q37">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="R37">
         <v>0</v>
@@ -10627,7 +10627,7 @@
         <v>2.38</v>
       </c>
       <c r="J38">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K38">
         <v>3.95</v>
@@ -10642,10 +10642,10 @@
         <v>5.7</v>
       </c>
       <c r="O38">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P38">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q38">
         <v>1.6</v>
@@ -10654,7 +10654,7 @@
         <v>1.64</v>
       </c>
       <c r="S38">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="T38">
         <v>1.53</v>
@@ -10708,7 +10708,7 @@
         <v>50</v>
       </c>
       <c r="AK38">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AL38">
         <v>34</v>
@@ -10717,7 +10717,7 @@
         <v>55</v>
       </c>
       <c r="AN38">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO38">
         <v>12.5</v>
@@ -10857,19 +10857,19 @@
         <v>332</v>
       </c>
       <c r="F39">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="G39">
-        <v>2.64</v>
+        <v>2.72</v>
       </c>
       <c r="H39">
+        <v>2.7</v>
+      </c>
+      <c r="I39">
         <v>2.78</v>
       </c>
-      <c r="I39">
-        <v>2.8</v>
-      </c>
       <c r="J39">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K39">
         <v>3.8</v>
@@ -10896,7 +10896,7 @@
         <v>1.55</v>
       </c>
       <c r="S39">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="T39">
         <v>1.59</v>
@@ -10926,7 +10926,7 @@
         <v>14.5</v>
       </c>
       <c r="AC39">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD39">
         <v>13</v>
@@ -10962,19 +10962,19 @@
         <v>16.5</v>
       </c>
       <c r="AO39">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AP39">
         <v>18</v>
       </c>
       <c r="AQ39">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AR39">
         <v>18.5</v>
       </c>
       <c r="AS39">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="AT39">
         <v>13</v>
@@ -10983,10 +10983,10 @@
         <v>8</v>
       </c>
       <c r="AV39">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AW39">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AX39">
         <v>17.5</v>
@@ -11019,55 +11019,55 @@
         <v>16</v>
       </c>
       <c r="BH39">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI39">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BJ39">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BK39">
         <v>1.01</v>
       </c>
       <c r="BL39">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM39">
         <v>1.01</v>
       </c>
       <c r="BN39">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO39">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BP39">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ39">
         <v>1.01</v>
       </c>
       <c r="BR39">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS39">
         <v>1.01</v>
       </c>
       <c r="BT39">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="BU39">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BV39">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BW39">
         <v>1.01</v>
       </c>
       <c r="BX39">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY39">
         <v>1.01</v>
@@ -11252,7 +11252,7 @@
         <v>19.5</v>
       </c>
       <c r="BE40">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF40">
         <v>7.6</v>
@@ -11341,16 +11341,16 @@
         <v>334</v>
       </c>
       <c r="F41">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G41">
         <v>1.64</v>
       </c>
       <c r="H41">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="I41">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="J41">
         <v>4.7</v>
@@ -11371,13 +11371,13 @@
         <v>1.17</v>
       </c>
       <c r="P41">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="Q41">
         <v>1.53</v>
       </c>
       <c r="R41">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="S41">
         <v>2.32</v>
@@ -11398,10 +11398,10 @@
         <v>36</v>
       </c>
       <c r="Y41">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="Z41">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA41">
         <v>150</v>
@@ -11425,13 +11425,13 @@
         <v>10.5</v>
       </c>
       <c r="AH41">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AI41">
         <v>70</v>
       </c>
       <c r="AJ41">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AK41">
         <v>15.5</v>
@@ -11458,7 +11458,7 @@
         <v>27</v>
       </c>
       <c r="AS41">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AT41">
         <v>12</v>
@@ -11479,7 +11479,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ41">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA41">
         <v>28</v>
@@ -11503,58 +11503,58 @@
         <v>27</v>
       </c>
       <c r="BH41">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BI41">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BJ41">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK41">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BL41">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BM41">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BN41">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO41">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BP41">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BQ41">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BR41">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS41">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BT41">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BU41">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BV41">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BW41">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BX41">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BY41">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BZ41">
         <v>0</v>
@@ -11586,7 +11586,7 @@
         <v>5.3</v>
       </c>
       <c r="G42">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="H42">
         <v>1.64</v>
@@ -11727,7 +11727,7 @@
         <v>20</v>
       </c>
       <c r="BB42">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BC42">
         <v>29</v>
@@ -11745,64 +11745,64 @@
         <v>5.6</v>
       </c>
       <c r="BH42">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BI42">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BJ42">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BK42">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BL42">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BM42">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BN42">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BO42">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BP42">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BQ42">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BR42">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS42">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BT42">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BU42">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="BV42">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BW42">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BX42">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BY42">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BZ42">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="CA42">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="CB42" t="s">
         <v>431</v>
@@ -12070,16 +12070,16 @@
         <v>2.98</v>
       </c>
       <c r="G44">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="H44">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="I44">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="J44">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="K44">
         <v>4.5</v>
@@ -12100,7 +12100,7 @@
         <v>2.12</v>
       </c>
       <c r="Q44">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R44">
         <v>0</v>
@@ -12554,10 +12554,10 @@
         <v>3.1</v>
       </c>
       <c r="G46">
-        <v>4.9</v>
+        <v>4.1</v>
       </c>
       <c r="H46">
-        <v>2.02</v>
+        <v>1.89</v>
       </c>
       <c r="I46">
         <v>2.54</v>
@@ -12566,7 +12566,7 @@
         <v>3.3</v>
       </c>
       <c r="K46">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="L46">
         <v>0</v>
@@ -12805,10 +12805,10 @@
         <v>2.24</v>
       </c>
       <c r="J47">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K47">
-        <v>100</v>
+        <v>4.9</v>
       </c>
       <c r="L47">
         <v>0</v>
@@ -12826,7 +12826,7 @@
         <v>1.64</v>
       </c>
       <c r="Q47">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R47">
         <v>0</v>
@@ -13277,10 +13277,10 @@
         <v>342</v>
       </c>
       <c r="F49">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="G49">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="H49">
         <v>2.72</v>
@@ -13289,7 +13289,7 @@
         <v>2.74</v>
       </c>
       <c r="J49">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K49">
         <v>3.75</v>
@@ -14003,16 +14003,16 @@
         <v>345</v>
       </c>
       <c r="F52">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="G52">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="H52">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="I52">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="J52">
         <v>3.6</v>
@@ -14033,10 +14033,10 @@
         <v>0</v>
       </c>
       <c r="P52">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="Q52">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R52">
         <v>0</v>
@@ -14520,7 +14520,7 @@
         <v>2.06</v>
       </c>
       <c r="Q54">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="R54">
         <v>0</v>
@@ -14741,7 +14741,7 @@
         <v>4</v>
       </c>
       <c r="J55">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K55">
         <v>3.9</v>
@@ -14759,7 +14759,7 @@
         <v>0</v>
       </c>
       <c r="P55">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="Q55">
         <v>1.86</v>
@@ -14974,10 +14974,10 @@
         <v>2.52</v>
       </c>
       <c r="G56">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H56">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="I56">
         <v>3.2</v>
@@ -15001,10 +15001,10 @@
         <v>0</v>
       </c>
       <c r="P56">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q56">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R56">
         <v>0</v>
@@ -15216,7 +15216,7 @@
         <v>2.52</v>
       </c>
       <c r="G57">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="H57">
         <v>2.96</v>
@@ -15243,10 +15243,10 @@
         <v>0</v>
       </c>
       <c r="P57">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q57">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R57">
         <v>0</v>
@@ -15455,7 +15455,7 @@
         <v>351</v>
       </c>
       <c r="F58">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G58">
         <v>2.32</v>
@@ -15464,7 +15464,7 @@
         <v>3.45</v>
       </c>
       <c r="I58">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J58">
         <v>3.5</v>
@@ -15485,7 +15485,7 @@
         <v>0</v>
       </c>
       <c r="P58">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="Q58">
         <v>2.08</v>
@@ -15709,7 +15709,7 @@
         <v>1.94</v>
       </c>
       <c r="J59">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K59">
         <v>4.2</v>
@@ -16181,13 +16181,13 @@
         <v>354</v>
       </c>
       <c r="F61">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="G61">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="H61">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I61">
         <v>4.6</v>
@@ -16205,7 +16205,7 @@
         <v>1.07</v>
       </c>
       <c r="N61">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O61">
         <v>1.31</v>
@@ -16235,10 +16235,10 @@
         <v>0</v>
       </c>
       <c r="X61">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y61">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z61">
         <v>34</v>
@@ -16247,7 +16247,7 @@
         <v>100</v>
       </c>
       <c r="AB61">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AC61">
         <v>8.199999999999999</v>
@@ -16259,7 +16259,7 @@
         <v>60</v>
       </c>
       <c r="AF61">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AG61">
         <v>10</v>
@@ -16274,7 +16274,7 @@
         <v>23</v>
       </c>
       <c r="AK61">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL61">
         <v>34</v>
@@ -16292,7 +16292,7 @@
         <v>13.5</v>
       </c>
       <c r="AQ61">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AR61">
         <v>22</v>
@@ -16304,7 +16304,7 @@
         <v>9</v>
       </c>
       <c r="AU61">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV61">
         <v>15.5</v>
@@ -16328,7 +16328,7 @@
         <v>20</v>
       </c>
       <c r="BC61">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="BD61">
         <v>22</v>
@@ -16337,7 +16337,7 @@
         <v>36</v>
       </c>
       <c r="BF61">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BG61">
         <v>29</v>
@@ -16346,7 +16346,7 @@
         <v>3.5</v>
       </c>
       <c r="BI61">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="BJ61">
         <v>9.6</v>
@@ -16358,28 +16358,28 @@
         <v>120</v>
       </c>
       <c r="BM61">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BN61">
         <v>4.7</v>
       </c>
       <c r="BO61">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BP61">
         <v>13.5</v>
       </c>
       <c r="BQ61">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR61">
         <v>27</v>
       </c>
       <c r="BS61">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BT61">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BU61">
         <v>6</v>
@@ -16388,13 +16388,13 @@
         <v>36</v>
       </c>
       <c r="BW61">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BX61">
         <v>44</v>
       </c>
       <c r="BY61">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ61">
         <v>23</v>
@@ -16465,7 +16465,7 @@
         <v>3.4</v>
       </c>
       <c r="T62">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U62">
         <v>2.2</v>
@@ -16483,7 +16483,7 @@
         <v>14.5</v>
       </c>
       <c r="Z62">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AA62">
         <v>75</v>
@@ -16495,7 +16495,7 @@
         <v>8</v>
       </c>
       <c r="AD62">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AE62">
         <v>42</v>
@@ -16513,7 +16513,7 @@
         <v>55</v>
       </c>
       <c r="AJ62">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK62">
         <v>23</v>
@@ -16576,7 +16576,7 @@
         <v>30</v>
       </c>
       <c r="BE62">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="BF62">
         <v>14</v>
@@ -16916,7 +16916,7 @@
         <v>3.7</v>
       </c>
       <c r="I64">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J64">
         <v>3.4</v>
@@ -16937,7 +16937,7 @@
         <v>0</v>
       </c>
       <c r="P64">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q64">
         <v>2.22</v>
@@ -17391,10 +17391,10 @@
         <v>359</v>
       </c>
       <c r="F66">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="G66">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="H66">
         <v>3.4</v>
@@ -17403,7 +17403,7 @@
         <v>3.65</v>
       </c>
       <c r="J66">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K66">
         <v>3.7</v>
@@ -17421,10 +17421,10 @@
         <v>0</v>
       </c>
       <c r="P66">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="Q66">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="R66">
         <v>0</v>
@@ -17633,22 +17633,22 @@
         <v>360</v>
       </c>
       <c r="F67">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G67">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="H67">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="I67">
-        <v>2.94</v>
+        <v>2.62</v>
       </c>
       <c r="J67">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="K67">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="L67">
         <v>0</v>
@@ -17663,10 +17663,10 @@
         <v>0</v>
       </c>
       <c r="P67">
-        <v>2.28</v>
+        <v>2.52</v>
       </c>
       <c r="Q67">
-        <v>1.43</v>
+        <v>1.52</v>
       </c>
       <c r="R67">
         <v>0</v>
@@ -17878,7 +17878,7 @@
         <v>2.74</v>
       </c>
       <c r="G68">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="H68">
         <v>2.86</v>
@@ -17905,7 +17905,7 @@
         <v>0</v>
       </c>
       <c r="P68">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="Q68">
         <v>2.3</v>
@@ -18117,16 +18117,16 @@
         <v>362</v>
       </c>
       <c r="F69">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G69">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="H69">
         <v>2.78</v>
       </c>
       <c r="I69">
-        <v>2.94</v>
+        <v>3.05</v>
       </c>
       <c r="J69">
         <v>3.85</v>
@@ -18147,10 +18147,10 @@
         <v>0</v>
       </c>
       <c r="P69">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q69">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="R69">
         <v>0</v>
@@ -18601,22 +18601,22 @@
         <v>364</v>
       </c>
       <c r="F71">
-        <v>2.7</v>
+        <v>2.96</v>
       </c>
       <c r="G71">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="H71">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="I71">
-        <v>2.76</v>
+        <v>2.54</v>
       </c>
       <c r="J71">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="K71">
-        <v>5.4</v>
+        <v>4.5</v>
       </c>
       <c r="L71">
         <v>0</v>
@@ -19360,19 +19360,19 @@
         <v>1.92</v>
       </c>
       <c r="Q74">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R74">
         <v>1.35</v>
       </c>
       <c r="S74">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T74">
         <v>1.8</v>
       </c>
       <c r="U74">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V74">
         <v>0</v>
@@ -19456,7 +19456,7 @@
         <v>10</v>
       </c>
       <c r="AW74">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX74">
         <v>21</v>
@@ -20083,7 +20083,7 @@
         <v>1.23</v>
       </c>
       <c r="P77">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q77">
         <v>1.7</v>
@@ -20095,7 +20095,7 @@
         <v>2.74</v>
       </c>
       <c r="T77">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="U77">
         <v>2.6</v>
@@ -20119,7 +20119,7 @@
         <v>30</v>
       </c>
       <c r="AB77">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AC77">
         <v>8.6</v>
@@ -20143,7 +20143,7 @@
         <v>29</v>
       </c>
       <c r="AJ77">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AK77">
         <v>44</v>
@@ -20155,7 +20155,7 @@
         <v>990</v>
       </c>
       <c r="AN77">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AO77">
         <v>12.5</v>
@@ -20185,13 +20185,13 @@
         <v>17.5</v>
       </c>
       <c r="AX77">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AY77">
         <v>13.5</v>
       </c>
       <c r="AZ77">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BA77">
         <v>19</v>
@@ -20200,10 +20200,10 @@
         <v>32</v>
       </c>
       <c r="BC77">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BD77">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BE77">
         <v>30</v>
@@ -20215,64 +20215,64 @@
         <v>11</v>
       </c>
       <c r="BH77">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI77">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BJ77">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK77">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BL77">
         <v>1000</v>
       </c>
       <c r="BM77">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN77">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO77">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BP77">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ77">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BR77">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS77">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BT77">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU77">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BV77">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BW77">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BX77">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="BY77">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BZ77">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA77">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="CB77" t="s">
         <v>431</v>
@@ -21263,40 +21263,40 @@
         <v>375</v>
       </c>
       <c r="F82">
+        <v>2.32</v>
+      </c>
+      <c r="G82">
+        <v>2.68</v>
+      </c>
+      <c r="H82">
+        <v>3.15</v>
+      </c>
+      <c r="I82">
+        <v>3.65</v>
+      </c>
+      <c r="J82">
+        <v>3.1</v>
+      </c>
+      <c r="K82">
+        <v>3.9</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82">
+        <v>0</v>
+      </c>
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82">
+        <v>0</v>
+      </c>
+      <c r="P82">
+        <v>1.62</v>
+      </c>
+      <c r="Q82">
         <v>2.16</v>
-      </c>
-      <c r="G82">
-        <v>3</v>
-      </c>
-      <c r="H82">
-        <v>2.82</v>
-      </c>
-      <c r="I82">
-        <v>4.3</v>
-      </c>
-      <c r="J82">
-        <v>3.05</v>
-      </c>
-      <c r="K82">
-        <v>5.5</v>
-      </c>
-      <c r="L82">
-        <v>0</v>
-      </c>
-      <c r="M82">
-        <v>0</v>
-      </c>
-      <c r="N82">
-        <v>0</v>
-      </c>
-      <c r="O82">
-        <v>0</v>
-      </c>
-      <c r="P82">
-        <v>1.54</v>
-      </c>
-      <c r="Q82">
-        <v>2.04</v>
       </c>
       <c r="R82">
         <v>0</v>
@@ -21505,22 +21505,22 @@
         <v>376</v>
       </c>
       <c r="F83">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="G83">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="H83">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="I83">
-        <v>4.9</v>
+        <v>4.3</v>
       </c>
       <c r="J83">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="K83">
-        <v>4.6</v>
+        <v>3.65</v>
       </c>
       <c r="L83">
         <v>0</v>
@@ -21535,10 +21535,10 @@
         <v>0</v>
       </c>
       <c r="P83">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="Q83">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="R83">
         <v>0</v>
@@ -21989,22 +21989,22 @@
         <v>378</v>
       </c>
       <c r="F85">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="G85">
-        <v>4.9</v>
+        <v>4</v>
       </c>
       <c r="H85">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="I85">
         <v>2.14</v>
       </c>
       <c r="J85">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="K85">
-        <v>5.1</v>
+        <v>3.95</v>
       </c>
       <c r="L85">
         <v>0</v>
@@ -22019,10 +22019,10 @@
         <v>0</v>
       </c>
       <c r="P85">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="Q85">
-        <v>1.71</v>
+        <v>1.86</v>
       </c>
       <c r="R85">
         <v>0</v>
@@ -22231,16 +22231,16 @@
         <v>379</v>
       </c>
       <c r="F86">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="G86">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="H86">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I86">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J86">
         <v>3.85</v>
@@ -22264,19 +22264,19 @@
         <v>2.32</v>
       </c>
       <c r="Q86">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R86">
         <v>1.52</v>
       </c>
       <c r="S86">
-        <v>2.84</v>
+        <v>2.82</v>
       </c>
       <c r="T86">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="U86">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="V86">
         <v>0</v>
@@ -22285,7 +22285,7 @@
         <v>0</v>
       </c>
       <c r="X86">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y86">
         <v>15</v>
@@ -22294,7 +22294,7 @@
         <v>25</v>
       </c>
       <c r="AA86">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB86">
         <v>12.5</v>
@@ -22321,7 +22321,7 @@
         <v>36</v>
       </c>
       <c r="AJ86">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AK86">
         <v>22</v>
@@ -22333,7 +22333,7 @@
         <v>60</v>
       </c>
       <c r="AN86">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO86">
         <v>23</v>
@@ -22375,19 +22375,19 @@
         <v>32</v>
       </c>
       <c r="BB86">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC86">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD86">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BE86">
         <v>50</v>
       </c>
       <c r="BF86">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BG86">
         <v>21</v>
@@ -22494,7 +22494,7 @@
         <v>0</v>
       </c>
       <c r="M87">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N87">
         <v>6</v>
@@ -22509,7 +22509,7 @@
         <v>1.53</v>
       </c>
       <c r="R87">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="S87">
         <v>2.3</v>
@@ -22527,7 +22527,7 @@
         <v>0</v>
       </c>
       <c r="X87">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y87">
         <v>42</v>
@@ -22542,7 +22542,7 @@
         <v>12</v>
       </c>
       <c r="AC87">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AD87">
         <v>38</v>
@@ -22566,7 +22566,7 @@
         <v>11.5</v>
       </c>
       <c r="AK87">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AL87">
         <v>32</v>
@@ -22584,10 +22584,10 @@
         <v>18.5</v>
       </c>
       <c r="AQ87">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR87">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AS87">
         <v>15</v>
@@ -22599,22 +22599,22 @@
         <v>12.5</v>
       </c>
       <c r="AV87">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW87">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AX87">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY87">
         <v>10</v>
       </c>
       <c r="AZ87">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA87">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BB87">
         <v>10</v>
@@ -22623,16 +22623,16 @@
         <v>12</v>
       </c>
       <c r="BD87">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE87">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BF87">
         <v>4.1</v>
       </c>
       <c r="BG87">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BH87">
         <v>1000</v>
@@ -22721,7 +22721,7 @@
         <v>2.38</v>
       </c>
       <c r="H88">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I88">
         <v>3.55</v>
@@ -22787,7 +22787,7 @@
         <v>7.6</v>
       </c>
       <c r="AD88">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AE88">
         <v>46</v>
@@ -22987,7 +22987,7 @@
         <v>1.44</v>
       </c>
       <c r="P89">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="Q89">
         <v>2.34</v>
@@ -23002,7 +23002,7 @@
         <v>1.98</v>
       </c>
       <c r="U89">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V89">
         <v>0</v>
@@ -23011,7 +23011,7 @@
         <v>0</v>
       </c>
       <c r="X89">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y89">
         <v>8.6</v>
@@ -23026,13 +23026,13 @@
         <v>11.5</v>
       </c>
       <c r="AC89">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD89">
         <v>12</v>
       </c>
       <c r="AE89">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF89">
         <v>23</v>
@@ -23041,7 +23041,7 @@
         <v>15</v>
       </c>
       <c r="AH89">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI89">
         <v>50</v>
@@ -23080,13 +23080,13 @@
         <v>10</v>
       </c>
       <c r="AU89">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV89">
         <v>10.5</v>
       </c>
       <c r="AW89">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AX89">
         <v>20</v>
@@ -23098,7 +23098,7 @@
         <v>18</v>
       </c>
       <c r="BA89">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="BB89">
         <v>32</v>
@@ -23107,16 +23107,16 @@
         <v>36</v>
       </c>
       <c r="BD89">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="BE89">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BF89">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="BG89">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BH89">
         <v>1000</v>
@@ -23211,7 +23211,7 @@
         <v>5.9</v>
       </c>
       <c r="J90">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K90">
         <v>4.3</v>
@@ -23223,19 +23223,19 @@
         <v>1.06</v>
       </c>
       <c r="N90">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O90">
         <v>1.28</v>
       </c>
       <c r="P90">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q90">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="R90">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S90">
         <v>3.15</v>
@@ -23256,13 +23256,13 @@
         <v>17.5</v>
       </c>
       <c r="Y90">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z90">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA90">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB90">
         <v>9.4</v>
@@ -23286,13 +23286,13 @@
         <v>21</v>
       </c>
       <c r="AI90">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ90">
         <v>17</v>
       </c>
       <c r="AK90">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AL90">
         <v>36</v>
@@ -23301,10 +23301,10 @@
         <v>130</v>
       </c>
       <c r="AN90">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO90">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AP90">
         <v>15</v>
@@ -23313,10 +23313,10 @@
         <v>17.5</v>
       </c>
       <c r="AR90">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="AS90">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT90">
         <v>8.6</v>
@@ -23349,16 +23349,16 @@
         <v>15</v>
       </c>
       <c r="BD90">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BE90">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="BF90">
         <v>8.4</v>
       </c>
       <c r="BG90">
-        <v>11.5</v>
+        <v>36</v>
       </c>
       <c r="BH90">
         <v>1000</v>
@@ -23683,22 +23683,22 @@
         <v>385</v>
       </c>
       <c r="F92">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="G92">
-        <v>1000</v>
+        <v>1.46</v>
       </c>
       <c r="H92">
-        <v>1.08</v>
+        <v>8</v>
       </c>
       <c r="I92">
-        <v>17</v>
+        <v>11.5</v>
       </c>
       <c r="J92">
         <v>5.3</v>
       </c>
       <c r="K92">
-        <v>950</v>
+        <v>6.4</v>
       </c>
       <c r="L92">
         <v>0</v>
@@ -23713,10 +23713,10 @@
         <v>0</v>
       </c>
       <c r="P92">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="Q92">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="R92">
         <v>0</v>
@@ -23958,7 +23958,7 @@
         <v>3.05</v>
       </c>
       <c r="Q93">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="R93">
         <v>0</v>
@@ -24167,22 +24167,22 @@
         <v>387</v>
       </c>
       <c r="F94">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="G94">
-        <v>2.68</v>
+        <v>2.46</v>
       </c>
       <c r="H94">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="I94">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="J94">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K94">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="L94">
         <v>0</v>
@@ -24197,10 +24197,10 @@
         <v>0</v>
       </c>
       <c r="P94">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="Q94">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="R94">
         <v>0</v>
@@ -24424,7 +24424,7 @@
         <v>3.15</v>
       </c>
       <c r="K95">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L95">
         <v>0</v>
@@ -24439,7 +24439,7 @@
         <v>0</v>
       </c>
       <c r="P95">
-        <v>1.61</v>
+        <v>1.59</v>
       </c>
       <c r="Q95">
         <v>2.38</v>
@@ -24681,10 +24681,10 @@
         <v>0</v>
       </c>
       <c r="P96">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q96">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="R96">
         <v>0</v>
@@ -24893,16 +24893,16 @@
         <v>390</v>
       </c>
       <c r="F97">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="G97">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="H97">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I97">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J97">
         <v>3.85</v>
@@ -24983,7 +24983,7 @@
         <v>60</v>
       </c>
       <c r="AJ97">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK97">
         <v>20</v>
@@ -25043,16 +25043,16 @@
         <v>17.5</v>
       </c>
       <c r="BD97">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BE97">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BF97">
         <v>11.5</v>
       </c>
       <c r="BG97">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BH97">
         <v>1000</v>
@@ -25135,19 +25135,19 @@
         <v>391</v>
       </c>
       <c r="F98">
-        <v>2.22</v>
+        <v>2.52</v>
       </c>
       <c r="G98">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="H98">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="I98">
         <v>3.65</v>
       </c>
       <c r="J98">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="K98">
         <v>3.6</v>
@@ -25377,7 +25377,7 @@
         <v>392</v>
       </c>
       <c r="F99">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G99">
         <v>2.1</v>
@@ -25386,7 +25386,7 @@
         <v>3.95</v>
       </c>
       <c r="I99">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="J99">
         <v>3.6</v>
@@ -25652,7 +25652,7 @@
         <v>1.62</v>
       </c>
       <c r="Q100">
-        <v>1.97</v>
+        <v>2.08</v>
       </c>
       <c r="R100">
         <v>0</v>
@@ -26103,22 +26103,22 @@
         <v>395</v>
       </c>
       <c r="F102">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="G102">
-        <v>2.74</v>
+        <v>2.46</v>
       </c>
       <c r="H102">
-        <v>2.66</v>
+        <v>2.86</v>
       </c>
       <c r="I102">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="J102">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="K102">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="L102">
         <v>0</v>
@@ -26133,10 +26133,10 @@
         <v>0</v>
       </c>
       <c r="P102">
-        <v>2.26</v>
+        <v>2.48</v>
       </c>
       <c r="Q102">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="R102">
         <v>0</v>
@@ -26354,13 +26354,13 @@
         <v>7.6</v>
       </c>
       <c r="I103">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J103">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K103">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="L103">
         <v>0</v>
@@ -26587,22 +26587,22 @@
         <v>397</v>
       </c>
       <c r="F104">
-        <v>1.06</v>
+        <v>2.88</v>
       </c>
       <c r="G104">
         <v>3.1</v>
       </c>
       <c r="H104">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="I104">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="J104">
-        <v>1.08</v>
+        <v>2.74</v>
       </c>
       <c r="K104">
-        <v>1000</v>
+        <v>2.96</v>
       </c>
       <c r="L104">
         <v>0</v>
@@ -26617,10 +26617,10 @@
         <v>0</v>
       </c>
       <c r="P104">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="Q104">
-        <v>2.92</v>
+        <v>3.15</v>
       </c>
       <c r="R104">
         <v>0</v>
@@ -26838,13 +26838,13 @@
         <v>5.1</v>
       </c>
       <c r="I105">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J105">
         <v>3.95</v>
       </c>
       <c r="K105">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L105">
         <v>0</v>
@@ -26859,10 +26859,10 @@
         <v>0</v>
       </c>
       <c r="P105">
-        <v>1.25</v>
+        <v>2.12</v>
       </c>
       <c r="Q105">
-        <v>1.03</v>
+        <v>1.71</v>
       </c>
       <c r="R105">
         <v>0</v>
@@ -27101,7 +27101,7 @@
         <v>0</v>
       </c>
       <c r="P106">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q106">
         <v>1.84</v>
@@ -27558,19 +27558,19 @@
         <v>3.45</v>
       </c>
       <c r="G108">
-        <v>5.4</v>
+        <v>4.1</v>
       </c>
       <c r="H108">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="I108">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="J108">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="K108">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="L108">
         <v>0</v>
@@ -27585,10 +27585,10 @@
         <v>0</v>
       </c>
       <c r="P108">
-        <v>2.26</v>
+        <v>2.48</v>
       </c>
       <c r="Q108">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="R108">
         <v>0</v>
@@ -28039,22 +28039,22 @@
         <v>403</v>
       </c>
       <c r="F110">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="G110">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="H110">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="I110">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="J110">
         <v>3.55</v>
       </c>
       <c r="K110">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="L110">
         <v>0</v>
@@ -28069,10 +28069,10 @@
         <v>0</v>
       </c>
       <c r="P110">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="Q110">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="R110">
         <v>0</v>
@@ -28284,13 +28284,13 @@
         <v>2.7</v>
       </c>
       <c r="G111">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="H111">
         <v>2.6</v>
       </c>
       <c r="I111">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="J111">
         <v>3.3</v>
@@ -28538,7 +28538,7 @@
         <v>3.8</v>
       </c>
       <c r="K112">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L112">
         <v>0</v>
@@ -28553,10 +28553,10 @@
         <v>0</v>
       </c>
       <c r="P112">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="Q112">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="R112">
         <v>0</v>
@@ -28765,16 +28765,16 @@
         <v>406</v>
       </c>
       <c r="F113">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="G113">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H113">
         <v>2.28</v>
       </c>
       <c r="I113">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="J113">
         <v>3.35</v>
@@ -28798,7 +28798,7 @@
         <v>1.8</v>
       </c>
       <c r="Q113">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R113">
         <v>0</v>
@@ -29249,7 +29249,7 @@
         <v>408</v>
       </c>
       <c r="F115">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="G115">
         <v>1.47</v>
@@ -29258,7 +29258,7 @@
         <v>8</v>
       </c>
       <c r="I115">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="J115">
         <v>5</v>
@@ -29506,7 +29506,7 @@
         <v>3.5</v>
       </c>
       <c r="K116">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L116">
         <v>0</v>
@@ -29736,7 +29736,7 @@
         <v>1.56</v>
       </c>
       <c r="G117">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="H117">
         <v>5.7</v>
@@ -29763,10 +29763,10 @@
         <v>0</v>
       </c>
       <c r="P117">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="Q117">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="R117">
         <v>0</v>
@@ -29975,22 +29975,22 @@
         <v>411</v>
       </c>
       <c r="F118">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="G118">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H118">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I118">
         <v>4.9</v>
       </c>
       <c r="J118">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K118">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="L118">
         <v>0</v>
@@ -29999,25 +29999,25 @@
         <v>1.08</v>
       </c>
       <c r="N118">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O118">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P118">
         <v>1.84</v>
       </c>
       <c r="Q118">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R118">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S118">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="T118">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="U118">
         <v>1.99</v>
@@ -30029,7 +30029,7 @@
         <v>0</v>
       </c>
       <c r="X118">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y118">
         <v>15</v>
@@ -30041,7 +30041,7 @@
         <v>140</v>
       </c>
       <c r="AB118">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC118">
         <v>8.4</v>
@@ -30077,7 +30077,7 @@
         <v>150</v>
       </c>
       <c r="AN118">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AO118">
         <v>85</v>
@@ -30092,13 +30092,13 @@
         <v>26</v>
       </c>
       <c r="AS118">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT118">
+        <v>7.6</v>
+      </c>
+      <c r="AU118">
         <v>7.4</v>
-      </c>
-      <c r="AU118">
-        <v>7.6</v>
       </c>
       <c r="AV118">
         <v>16.5</v>
@@ -30116,7 +30116,7 @@
         <v>18</v>
       </c>
       <c r="BA118">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BB118">
         <v>18.5</v>
@@ -30128,13 +30128,13 @@
         <v>29</v>
       </c>
       <c r="BE118">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BF118">
         <v>12.5</v>
       </c>
       <c r="BG118">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BH118">
         <v>1000</v>
@@ -30232,7 +30232,7 @@
         <v>7.2</v>
       </c>
       <c r="K119">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="L119">
         <v>0</v>
@@ -30241,7 +30241,7 @@
         <v>1.04</v>
       </c>
       <c r="N119">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="O119">
         <v>1.23</v>
@@ -30250,7 +30250,7 @@
         <v>2.34</v>
       </c>
       <c r="Q119">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="R119">
         <v>1.51</v>
@@ -30304,7 +30304,7 @@
         <v>50</v>
       </c>
       <c r="AI119">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="AJ119">
         <v>8.6</v>
@@ -30319,7 +30319,7 @@
         <v>420</v>
       </c>
       <c r="AN119">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AO119">
         <v>1000</v>
@@ -30331,10 +30331,10 @@
         <v>32</v>
       </c>
       <c r="AR119">
+        <v>11.5</v>
+      </c>
+      <c r="AS119">
         <v>12</v>
-      </c>
-      <c r="AS119">
-        <v>13</v>
       </c>
       <c r="AT119">
         <v>7.4</v>
@@ -30346,7 +30346,7 @@
         <v>29</v>
       </c>
       <c r="AW119">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AX119">
         <v>6.2</v>
@@ -30358,7 +30358,7 @@
         <v>40</v>
       </c>
       <c r="BA119">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BB119">
         <v>7.4</v>
@@ -30370,13 +30370,13 @@
         <v>28</v>
       </c>
       <c r="BE119">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BF119">
         <v>4.2</v>
       </c>
       <c r="BG119">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BH119">
         <v>1000</v>
@@ -30483,7 +30483,7 @@
         <v>1.08</v>
       </c>
       <c r="N120">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O120">
         <v>1.37</v>
@@ -30513,13 +30513,13 @@
         <v>0</v>
       </c>
       <c r="X120">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y120">
         <v>14.5</v>
       </c>
       <c r="Z120">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA120">
         <v>1000</v>
@@ -30543,19 +30543,19 @@
         <v>10.5</v>
       </c>
       <c r="AH120">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AI120">
         <v>80</v>
       </c>
       <c r="AJ120">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AK120">
         <v>23</v>
       </c>
       <c r="AL120">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM120">
         <v>1000</v>
@@ -30600,7 +30600,7 @@
         <v>17.5</v>
       </c>
       <c r="BA120">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB120">
         <v>20</v>
@@ -30612,7 +30612,7 @@
         <v>30</v>
       </c>
       <c r="BE120">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF120">
         <v>14</v>
@@ -30704,7 +30704,7 @@
         <v>2.88</v>
       </c>
       <c r="G121">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H121">
         <v>2.38</v>
@@ -30943,7 +30943,7 @@
         <v>415</v>
       </c>
       <c r="F122">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="G122">
         <v>1.53</v>
@@ -30952,7 +30952,7 @@
         <v>7.4</v>
       </c>
       <c r="I122">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="J122">
         <v>4.8</v>
@@ -30967,7 +30967,7 @@
         <v>1.05</v>
       </c>
       <c r="N122">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O122">
         <v>1.27</v>
@@ -30985,7 +30985,7 @@
         <v>3.05</v>
       </c>
       <c r="T122">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="U122">
         <v>1.94</v>
@@ -31003,13 +31003,13 @@
         <v>25</v>
       </c>
       <c r="Z122">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AA122">
         <v>260</v>
       </c>
       <c r="AB122">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC122">
         <v>11</v>
@@ -31033,7 +31033,7 @@
         <v>110</v>
       </c>
       <c r="AJ122">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AK122">
         <v>16</v>
@@ -31057,10 +31057,10 @@
         <v>21</v>
       </c>
       <c r="AR122">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AS122">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AT122">
         <v>7.8</v>
@@ -31069,10 +31069,10 @@
         <v>9.4</v>
       </c>
       <c r="AV122">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AW122">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AX122">
         <v>8.199999999999999</v>
@@ -31084,7 +31084,7 @@
         <v>21</v>
       </c>
       <c r="BA122">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BB122">
         <v>12</v>
@@ -31096,13 +31096,13 @@
         <v>30</v>
       </c>
       <c r="BE122">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BF122">
         <v>6.6</v>
       </c>
       <c r="BG122">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH122">
         <v>1000</v>
@@ -31188,10 +31188,10 @@
         <v>2.8</v>
       </c>
       <c r="G123">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="H123">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="I123">
         <v>2.8</v>
@@ -31209,7 +31209,7 @@
         <v>1.08</v>
       </c>
       <c r="N123">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O123">
         <v>1.35</v>
@@ -31227,10 +31227,10 @@
         <v>3.65</v>
       </c>
       <c r="T123">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U123">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V123">
         <v>0</v>
@@ -31260,7 +31260,7 @@
         <v>13</v>
       </c>
       <c r="AE123">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AF123">
         <v>19</v>
@@ -31323,19 +31323,19 @@
         <v>11.5</v>
       </c>
       <c r="AZ123">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA123">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BB123">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BC123">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD123">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BE123">
         <v>10.5</v>
@@ -31675,16 +31675,16 @@
         <v>4.7</v>
       </c>
       <c r="H125">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="I125">
         <v>1.86</v>
       </c>
       <c r="J125">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K125">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="L125">
         <v>0</v>
@@ -31699,10 +31699,10 @@
         <v>0</v>
       </c>
       <c r="P125">
-        <v>2.56</v>
+        <v>2.84</v>
       </c>
       <c r="Q125">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="R125">
         <v>0</v>
@@ -31911,22 +31911,22 @@
         <v>419</v>
       </c>
       <c r="F126">
+        <v>3.15</v>
+      </c>
+      <c r="G126">
+        <v>3.55</v>
+      </c>
+      <c r="H126">
+        <v>2.48</v>
+      </c>
+      <c r="I126">
         <v>2.76</v>
       </c>
-      <c r="G126">
-        <v>4</v>
-      </c>
-      <c r="H126">
-        <v>2.28</v>
-      </c>
-      <c r="I126">
-        <v>3.1</v>
-      </c>
       <c r="J126">
-        <v>2.86</v>
+        <v>2.98</v>
       </c>
       <c r="K126">
-        <v>5.1</v>
+        <v>3.6</v>
       </c>
       <c r="L126">
         <v>0</v>
@@ -31941,10 +31941,10 @@
         <v>0</v>
       </c>
       <c r="P126">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="Q126">
-        <v>2.24</v>
+        <v>2.42</v>
       </c>
       <c r="R126">
         <v>0</v>
@@ -32156,16 +32156,16 @@
         <v>1.96</v>
       </c>
       <c r="G127">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H127">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I127">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="J127">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K127">
         <v>3.5</v>
@@ -32183,10 +32183,10 @@
         <v>0</v>
       </c>
       <c r="P127">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q127">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="R127">
         <v>0</v>
@@ -32395,22 +32395,22 @@
         <v>421</v>
       </c>
       <c r="F128">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="G128">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="H128">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="I128">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="J128">
-        <v>2.82</v>
+        <v>3</v>
       </c>
       <c r="K128">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="L128">
         <v>0</v>
@@ -32425,10 +32425,10 @@
         <v>0</v>
       </c>
       <c r="P128">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="Q128">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R128">
         <v>0</v>
@@ -32652,7 +32652,7 @@
         <v>3.55</v>
       </c>
       <c r="K129">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L129">
         <v>0</v>
@@ -32664,7 +32664,7 @@
         <v>3.65</v>
       </c>
       <c r="O129">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P129">
         <v>1.92</v>
@@ -32706,7 +32706,7 @@
         <v>13.5</v>
       </c>
       <c r="AC129">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AD129">
         <v>11</v>
@@ -32775,7 +32775,7 @@
         <v>14</v>
       </c>
       <c r="AZ129">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA129">
         <v>24</v>
@@ -32885,16 +32885,16 @@
         <v>2.2</v>
       </c>
       <c r="H130">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="I130">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J130">
         <v>3.35</v>
       </c>
       <c r="K130">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L130">
         <v>0</v>
@@ -32909,7 +32909,7 @@
         <v>0</v>
       </c>
       <c r="P130">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="Q130">
         <v>2.06</v>
@@ -33121,19 +33121,19 @@
         <v>424</v>
       </c>
       <c r="F131">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="G131">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H131">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="I131">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="J131">
-        <v>1.1</v>
+        <v>3.9</v>
       </c>
       <c r="K131">
         <v>4.4</v>
@@ -33605,7 +33605,7 @@
         <v>426</v>
       </c>
       <c r="F133">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="G133">
         <v>2.02</v>
@@ -33614,10 +33614,10 @@
         <v>4.9</v>
       </c>
       <c r="I133">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J133">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K133">
         <v>3.7</v>
@@ -33635,10 +33635,10 @@
         <v>0</v>
       </c>
       <c r="P133">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q133">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R133">
         <v>0</v>
@@ -33853,7 +33853,7 @@
         <v>3.55</v>
       </c>
       <c r="H134">
-        <v>2.46</v>
+        <v>2.4</v>
       </c>
       <c r="I134">
         <v>2.74</v>
@@ -33862,7 +33862,7 @@
         <v>3.1</v>
       </c>
       <c r="K134">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="L134">
         <v>0</v>
@@ -33877,7 +33877,7 @@
         <v>0</v>
       </c>
       <c r="P134">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q134">
         <v>2.2</v>
